--- a/news_daily/2026-09-21.xlsx
+++ b/news_daily/2026-09-21.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -999,6 +1023,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1049,13 +1077,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1104,7 +1136,11 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>915ab6e906c64f52bf836f932763033b</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>61412df32eb735362cda9321</t>
@@ -1125,7 +1161,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -1161,6 +1201,18 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1201,7 +1253,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -1211,13 +1263,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1257,7 +1313,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
@@ -1266,7 +1322,11 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>37025aa0a8c148eb94677bd1b3b93d33</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>54b66a8eb311aa2d60112dec</t>
@@ -1287,7 +1347,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -1323,6 +1387,22 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1493,6 +1573,10 @@
         </is>
       </c>
       <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr"/>
+      <c r="BL5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1663,6 +1747,10 @@
         </is>
       </c>
       <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr"/>
+      <c r="BL6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1703,7 +1791,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1713,13 +1801,17 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1759,7 +1851,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1768,7 +1860,11 @@
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>36d78775c80e40ca9e11941c8b5ea791</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>b8c7d71d838213ae9dc3ad8a</t>
@@ -1789,7 +1885,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -1825,6 +1925,22 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1875,13 +1991,17 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1930,7 +2050,11 @@
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>b20c73dea8bf405296c2316e6afe1e27</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
           <t>1799511b1512252d33cf0197</t>
@@ -1951,7 +2075,11 @@
       <c r="AL8" s="3" t="inlineStr"/>
       <c r="AM8" s="3" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="3" t="inlineStr"/>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr"/>
@@ -1987,6 +2115,18 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2027,7 +2167,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2037,13 +2177,17 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -2083,7 +2227,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
@@ -2092,7 +2236,11 @@
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>9808ad7df1984fcd940a81e0158ab36e</t>
+        </is>
+      </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
           <t>a47b1fdbd89dc50c858ad0a2</t>
@@ -2113,7 +2261,11 @@
       <c r="AL9" s="3" t="inlineStr"/>
       <c r="AM9" s="3" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="3" t="inlineStr"/>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr"/>
@@ -2149,6 +2301,22 @@
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2189,7 +2357,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -2199,13 +2367,17 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2245,7 +2417,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -2254,7 +2426,11 @@
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>a42b5d7968494bcbb2b0a48cd57ba906</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>6b7f326907ffa4a5792270ed</t>
@@ -2275,7 +2451,11 @@
       <c r="AL10" s="3" t="inlineStr"/>
       <c r="AM10" s="3" t="inlineStr"/>
       <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="3" t="inlineStr"/>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr"/>
@@ -2311,9 +2491,25 @@
         </is>
       </c>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH10"/>
+  <autoFilter ref="A1:BL10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2324,7 +2520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH8"/>
+  <dimension ref="A1:BL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2387,6 +2583,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2688,6 +2888,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -2860,6 +3080,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2910,13 +3134,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -2965,7 +3193,11 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>915ab6e906c64f52bf836f932763033b</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>61412df32eb735362cda9321</t>
@@ -2986,7 +3218,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -3022,6 +3258,18 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3062,7 +3310,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -3072,13 +3320,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -3118,7 +3370,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
@@ -3127,7 +3379,11 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>37025aa0a8c148eb94677bd1b3b93d33</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>54b66a8eb311aa2d60112dec</t>
@@ -3148,7 +3404,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -3184,6 +3444,22 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3224,7 +3500,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -3234,13 +3510,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -3280,7 +3560,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -3289,7 +3569,11 @@
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>36d78775c80e40ca9e11941c8b5ea791</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>b8c7d71d838213ae9dc3ad8a</t>
@@ -3310,7 +3594,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -3346,6 +3634,22 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -3396,13 +3700,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -3451,7 +3759,11 @@
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>b20c73dea8bf405296c2316e6afe1e27</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>1799511b1512252d33cf0197</t>
@@ -3472,7 +3784,11 @@
       <c r="AL6" s="3" t="inlineStr"/>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="3" t="inlineStr"/>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
@@ -3508,6 +3824,18 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -3548,7 +3876,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -3558,13 +3886,17 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -3604,7 +3936,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -3613,7 +3945,11 @@
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>9808ad7df1984fcd940a81e0158ab36e</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>a47b1fdbd89dc50c858ad0a2</t>
@@ -3634,7 +3970,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -3670,6 +4010,22 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -3710,7 +4066,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -3720,13 +4076,17 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -3766,7 +4126,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -3775,7 +4135,11 @@
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>a42b5d7968494bcbb2b0a48cd57ba906</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
           <t>6b7f326907ffa4a5792270ed</t>
@@ -3796,7 +4160,11 @@
       <c r="AL8" s="3" t="inlineStr"/>
       <c r="AM8" s="3" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="3" t="inlineStr"/>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr"/>
@@ -3832,9 +4200,25 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH8"/>
+  <autoFilter ref="A1:BL8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3845,7 +4229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3908,6 +4292,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4211,9 +4599,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4224,7 +4632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4287,6 +4695,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4590,9 +5002,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4603,7 +5035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4653,134 +5085,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -4790,46 +5222,80 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="4" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
+      <c r="M2" s="4" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="4" t="inlineStr"/>
       <c r="Y2" s="4" t="inlineStr"/>
       <c r="Z2" s="4" t="inlineStr"/>
@@ -4838,12 +5304,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4853,90 +5319,94 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="4" t="inlineStr"/>
+      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="Z3" s="4" t="inlineStr"/>
+      <c r="AA3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -4946,94 +5416,94 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="4" t="inlineStr"/>
+      <c r="Y4" s="4" t="inlineStr"/>
+      <c r="Z4" s="4" t="inlineStr"/>
+      <c r="AA4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -5041,89 +5511,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="4" t="n">
+      <c r="AA5" s="4" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="4" t="inlineStr"/>
+      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="Z6" s="4" t="inlineStr"/>
+      <c r="AA6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="4" t="inlineStr"/>
+      <c r="Y7" s="4" t="inlineStr"/>
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="4" t="inlineStr"/>
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="AA8" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-09-21.xlsx
+++ b/news_daily/2026-09-21.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,18 +79,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -888,28 +880,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>供應鏈中斷</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -949,7 +945,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -958,7 +954,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>0709a50953cb47cbaca0875feb758158</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>458dc1a4d566398734bb40ca</t>
@@ -979,7 +979,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1023,10 +1027,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1405,352 +1421,352 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>CIEN</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Ciena Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-09-21T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Ciena upgraded, Flutter downgraded: Wall Street's top analyst calls</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>'-0.015</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNOEV5MWJGUE4yaWduUU0tVzhURjRuTkY0aVlVRV9ZWFN2aWNkWlRuTWZMTzJuWkh5Vk5FbUtkY2hOUTQ1eVd5S2dtaEZVcGo2ck1rcWRscTVzODRvbnNtV3JJY2pVQnZGeElwckNETklwTGhXSjl5Q3hlZ2poRWVCYnVkWURLOUFrNW9ydzdGaWp4NENmeVg3dDNTblpEM3JSZHI3TE5n?oc=5</t>
         </is>
       </c>
-      <c r="V5" s="4" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>bc98077090826b8e08d0e5a4</t>
         </is>
       </c>
-      <c r="AD5" s="4" t="inlineStr">
+      <c r="AD5" s="2" t="inlineStr">
         <is>
           <t>a27604ebf4f62e2cd1911e73</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr">
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
+      <c r="AX5" s="2" t="inlineStr"/>
+      <c r="AY5" s="2" t="inlineStr"/>
+      <c r="AZ5" s="2" t="inlineStr"/>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr">
         <is>
           <t>CIEN</t>
         </is>
       </c>
-      <c r="BC5" s="4" t="inlineStr">
+      <c r="BC5" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="4" t="inlineStr"/>
-      <c r="BE5" s="4" t="inlineStr">
+      <c r="BD5" s="2" t="inlineStr"/>
+      <c r="BE5" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="4" t="inlineStr">
+      <c r="BF5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="4" t="inlineStr">
+      <c r="BG5" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="4" t="inlineStr"/>
-      <c r="BI5" s="4" t="inlineStr"/>
-      <c r="BJ5" s="4" t="inlineStr"/>
-      <c r="BK5" s="4" t="inlineStr"/>
-      <c r="BL5" s="4" t="inlineStr"/>
+      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>EBAY</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>eBay Inc.</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-09-21T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>eBay Upgraded, Airbnb Downgraded: Updated Rankings on Top Blue-Chip Stocks</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>'-0.224</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQaDItSGl4Q0EyNFJFMWVyQUVCaXRWLXozeVdwWVA4VUEwZHMtb2J4eTJJT0k2MTZfUWVFc3lPeUNCNFpLbTJHZ01pczhqM3cxSWlqcE1XdWkwZy1Oak80S0lZX2p2UTlRVDVpbHI3M2xEdUVDZS15NVU0ZnVPdlNrSUE0NzJqT3h0NU5HMGVuNzNtUkczb2lxMUZJVHlQaHhuTkJZX0kzaw?oc=5</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>0f89c4f7092d29c6badbd804</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AD6" s="2" t="inlineStr">
         <is>
           <t>c4775c9b875b71e48fcc79cc</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr">
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
         <is>
           <t>EBAY</t>
         </is>
       </c>
-      <c r="BC6" s="4" t="inlineStr">
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="4" t="inlineStr">
+      <c r="BF6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="4" t="inlineStr">
+      <c r="BG6" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="4" t="inlineStr"/>
-      <c r="BI6" s="4" t="inlineStr"/>
-      <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr"/>
-      <c r="BL6" s="4" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2520,7 +2536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL8"/>
+  <dimension ref="A1:BL7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2912,178 +2928,190 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>KKR</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>KKR &amp; Co. Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>2026-09-21T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>KKR Bets on Korea AI Supply Chain After Record $3 Billion Deals</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>WGA Settles Antitrust Lawsuit With Paramount Over Warner Bros. Discovery Merger</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>反壟斷調查</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>'-0.858</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQVzdnN1pEMWZrZ214Q2JoQUpyaVExaTJ4aWJVdi1uM3dHZkx4dzNwWkJ1M0JlcVptMkV0Y1ktWlNPaHZQMDZ4amRoem1vZnpLRHNxZW5sNUpjZ19hV25aTHZmeFBZbDZZc1hIbjRSVG9oUkFVcUVPbjMxbWFIQmlTZURSRHpvbEZKdFJOLXI4dWpWdEJCVkFhSmZCNk13czcxamVyU3p0aw?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Variety</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>ANTITRUST_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>antitrust</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>915ab6e906c64f52bf836f932763033b</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>61412df32eb735362cda9321</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>0c52b19c295595679e0b6174</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr"/>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0.754</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQWXdweTVtcHc0TDFVZUMxN2I0NS1xRXFhQUFoNFNSVXpPUFRPWkdMMjJrcnlpYUR3NnVVT3pvc3FRMGZBb1hDZ1RmazBsbXVpYW9DeHdyTUVTTThXMjgxM3YtQVJPOEZiMkFMbTVXZDdJWHc5Nm9IUnZUc1o5QVdTdGY1YTl3b1ZwUVNTRHdtajZOSUJnSE03cG1WWGdhNExnYkJGT0VwZmpIX1ZzY0U4Um5TMA?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Bloomberg.com</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>458dc1a4d566398734bb40ca</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>3bf53bb95fa4e2937f6c9438</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>KKR</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr"/>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr"/>
+      <c r="AX2" s="3" t="inlineStr"/>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="BC2" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD2" s="2" t="inlineStr"/>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BD2" s="3" t="inlineStr"/>
+      <c r="BE2" s="3" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF2" s="3" t="inlineStr"/>
+      <c r="BG2" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3113,7 +3141,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>WGA Settles Antitrust Lawsuit With Paramount Over Warner Bros. Discovery Merger</t>
+          <t>Paramount reaches historic settlement with states, clearing way for WBD deal</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -3154,7 +3182,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>'-0.858</t>
+          <t>0.902</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr"/>
@@ -3168,12 +3196,12 @@
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQVzdnN1pEMWZrZ214Q2JoQUpyaVExaTJ4aWJVdi1uM3dHZkx4dzNwWkJ1M0JlcVptMkV0Y1ktWlNPaHZQMDZ4amRoem1vZnpLRHNxZW5sNUpjZ19hV25aTHZmeFBZbDZZc1hIbjRSVG9oUkFVcUVPbjMxbWFIQmlTZURSRHpvbEZKdFJOLXI4dWpWdEJCVkFhSmZCNk13czcxamVyU3p0aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1HWFZWdndMRk1qek1nVVUzclVjNnpTbzhPdWxKMTJWOTBJNTFEa1F3NHVtaWJQdmktRHlSTXNwdVlhWU44eEFrSHg3bjJiU0ZhSE9EU0xvbGRIM0pmbUd6VXNaMGtWSy1GUUY5alZGT0FUQUJCZ0VaYVdCWQ?oc=5</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>Variety</t>
+          <t>Axios</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr"/>
@@ -3189,23 +3217,23 @@
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>antitrust</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>915ab6e906c64f52bf836f932763033b</t>
+          <t>37025aa0a8c148eb94677bd1b3b93d33</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>61412df32eb735362cda9321</t>
+          <t>54b66a8eb311aa2d60112dec</t>
         </is>
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>0c52b19c295595679e0b6174</t>
+          <t>041fc3ec1c69f315947bab8c</t>
         </is>
       </c>
       <c r="AE3" s="3" t="inlineStr"/>
@@ -3258,7 +3286,11 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="3" t="inlineStr"/>
       <c r="BK3" s="3" t="inlineStr">
         <is>
@@ -3299,7 +3331,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Paramount reaches historic settlement with states, clearing way for WBD deal</t>
+          <t>Paramount-WBD Settlement Sets Up Editorial Independence Board For CNN And CBS News</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -3340,7 +3372,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>0.039</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr"/>
@@ -3354,12 +3386,12 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1HWFZWdndMRk1qek1nVVUzclVjNnpTbzhPdWxKMTJWOTBJNTFEa1F3NHVtaWJQdmktRHlSTXNwdVlhWU44eEFrSHg3bjJiU0ZhSE9EU0xvbGRIM0pmbUd6VXNaMGtWSy1GUUY5alZGT0FUQUJCZ0VaYVdCWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQNmYzZ1B3WXVOeWN3NVdvZ2tIdXowQVh3UW1KQ2FXRzhERTFyaUJIOEtmVkQ3aEN2MnVrbWM5UzhYWlI4NUZEWjNNRWpORzRhSkdyYWtER1NPRXBKbVdhRXN1VUw1dGdCSGVxRFZUNGkxUzRWN0xBai1KT20tS3BNRDBVUV9lWFRwWXc?oc=5</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>Axios</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr"/>
@@ -3381,17 +3413,17 @@
       <c r="AA4" s="3" t="inlineStr"/>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>37025aa0a8c148eb94677bd1b3b93d33</t>
+          <t>36d78775c80e40ca9e11941c8b5ea791</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>54b66a8eb311aa2d60112dec</t>
+          <t>b8c7d71d838213ae9dc3ad8a</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>041fc3ec1c69f315947bab8c</t>
+          <t>a0febc1feecd8d29bf52e4ab</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr"/>
@@ -3489,7 +3521,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Paramount-WBD Settlement Sets Up Editorial Independence Board For CNN And CBS News</t>
+          <t>Done! Paramount Settles Antitrust Suit, Set To Seal Deal For Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -3530,7 +3562,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.285</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr"/>
@@ -3544,7 +3576,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQNmYzZ1B3WXVOeWN3NVdvZ2tIdXowQVh3UW1KQ2FXRzhERTFyaUJIOEtmVkQ3aEN2MnVrbWM5UzhYWlI4NUZEWjNNRWpORzRhSkdyYWtER1NPRXBKbVdhRXN1VUw1dGdCSGVxRFZUNGkxUzRWN0xBai1KT20tS3BNRDBVUV9lWFRwWXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQenItbGpiREg1UUY3MktDTGpBTWY5Tk5YbENlLXZDNFZoWTJweFJ0U3NXdWVMOFVlUU4zVnVrSDNLeHhzQlZQaVZRd2JPZm4yQmtEYTBPZVFNRjV0OWNKLWk4RUFaUDQ4MVJPczdCTmlrd0Z5bEtYQm01RGdFTFZFV2pIWTZTY1JRN2pHNnl6OWhUN3EyODM4R3hFNldHT0U?oc=5</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
@@ -3565,23 +3597,23 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>antitrust</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr"/>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>36d78775c80e40ca9e11941c8b5ea791</t>
+          <t>b20c73dea8bf405296c2316e6afe1e27</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>b8c7d71d838213ae9dc3ad8a</t>
+          <t>1799511b1512252d33cf0197</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>a0febc1feecd8d29bf52e4ab</t>
+          <t>b25f271fb4a08bb93d42202f</t>
         </is>
       </c>
       <c r="AE5" s="3" t="inlineStr"/>
@@ -3634,11 +3666,7 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
-      <c r="BI5" s="3" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
+      <c r="BI5" s="3" t="inlineStr"/>
       <c r="BJ5" s="3" t="inlineStr"/>
       <c r="BK5" s="3" t="inlineStr">
         <is>
@@ -3679,7 +3707,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Done! Paramount Settles Antitrust Suit, Set To Seal Deal For Warner Bros. Discovery</t>
+          <t>Read the memo that Paramount CEO David Ellison sent to staffers after 2 settlements cleared the way for his WBD deal</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -3720,7 +3748,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr"/>
@@ -3734,12 +3762,12 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQenItbGpiREg1UUY3MktDTGpBTWY5Tk5YbENlLXZDNFZoWTJweFJ0U3NXdWVMOFVlUU4zVnVrSDNLeHhzQlZQaVZRd2JPZm4yQmtEYTBPZVFNRjV0OWNKLWk4RUFaUDQ4MVJPczdCTmlrd0Z5bEtYQm01RGdFTFZFV2pIWTZTY1JRN2pHNnl6OWhUN3EyODM4R3hFNldHT0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWC1Ea2lYbUVEVkh2UXoxZnN0NHFFOEZrd3RUeEx3b0JidHZNck9PLXNMTXRBQUw5eWYxQ2RKdWMtMm9SVVZaMlBJOUxLYWRwVWItME9KTGtqb1U2N1dDNHNhMUVDSEcyUDFmNnlIbDRRcE5zeVFfZjdHWXpyNXUxaFd4SUw4aG5uUEZQVDQtRFhLbnltODV5eVhZdG5uODdPcmdWUVJ2Yw?oc=5</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Business Insider</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr"/>
@@ -3755,23 +3783,23 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>antitrust</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr"/>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>b20c73dea8bf405296c2316e6afe1e27</t>
+          <t>9808ad7df1984fcd940a81e0158ab36e</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>1799511b1512252d33cf0197</t>
+          <t>a47b1fdbd89dc50c858ad0a2</t>
         </is>
       </c>
       <c r="AD6" s="3" t="inlineStr">
         <is>
-          <t>b25f271fb4a08bb93d42202f</t>
+          <t>764c03ea3ab9d26a9c59a984</t>
         </is>
       </c>
       <c r="AE6" s="3" t="inlineStr"/>
@@ -3824,7 +3852,11 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
       <c r="BJ6" s="3" t="inlineStr"/>
       <c r="BK6" s="3" t="inlineStr">
         <is>
@@ -3865,7 +3897,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Read the memo that Paramount CEO David Ellison sent to staffers after 2 settlements cleared the way for his WBD deal</t>
+          <t>David Ellison Reacts To Paramount-WBD Settlement With State AGs</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -3906,7 +3938,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>0.068</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr"/>
@@ -3920,12 +3952,12 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWC1Ea2lYbUVEVkh2UXoxZnN0NHFFOEZrd3RUeEx3b0JidHZNck9PLXNMTXRBQUw5eWYxQ2RKdWMtMm9SVVZaMlBJOUxLYWRwVWItME9KTGtqb1U2N1dDNHNhMUVDSEcyUDFmNnlIbDRRcE5zeVFfZjdHWXpyNXUxaFd4SUw4aG5uUEZQVDQtRFhLbnltODV5eVhZdG5uODdPcmdWUVJ2Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQRXZqMUdIczJKN29ScmFUOGhNNmVLM3ZyNjN5QkMxWjR6RFByTE8xOFhIUmlQanpNMkVHRDRhN2hvSm9UTU9udWtjVV9fNTRkLTFQLXlKZktXLUN1YmZFVEhmdVR4YldOc3hMZDlWYW1ucWcxY1lfd21YakJZSlZObi0tdVFNNlhaVlcwTkFkYlNKYnVXY1RtZl90NXJDVE0?oc=5</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>Business Insider</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr"/>
@@ -3947,17 +3979,17 @@
       <c r="AA7" s="3" t="inlineStr"/>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>9808ad7df1984fcd940a81e0158ab36e</t>
+          <t>a42b5d7968494bcbb2b0a48cd57ba906</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>a47b1fdbd89dc50c858ad0a2</t>
+          <t>6b7f326907ffa4a5792270ed</t>
         </is>
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>764c03ea3ab9d26a9c59a984</t>
+          <t>db17b926dd5c3b2eef2c21ed</t>
         </is>
       </c>
       <c r="AE7" s="3" t="inlineStr"/>
@@ -4027,198 +4059,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>David Ellison Reacts To Paramount-WBD Settlement With State AGs</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>0.068</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQRXZqMUdIczJKN29ScmFUOGhNNmVLM3ZyNjN5QkMxWjR6RFByTE8xOFhIUmlQanpNMkVHRDRhN2hvSm9UTU9udWtjVV9fNTRkLTFQLXlKZktXLUN1YmZFVEhmdVR4YldOc3hMZDlWYW1ucWcxY1lfd21YakJZSlZObi0tdVFNNlhaVlcwTkFkYlNKYnVXY1RtZl90NXJDVE0?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr">
-        <is>
-          <t>a42b5d7968494bcbb2b0a48cd57ba906</t>
-        </is>
-      </c>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>6b7f326907ffa4a5792270ed</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>db17b926dd5c3b2eef2c21ed</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr"/>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="BC8" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF8" s="3" t="inlineStr"/>
-      <c r="BG8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
-      <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL8"/>
+  <autoFilter ref="A1:BL7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5205,645 +5047,645 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-26</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H2" s="4" t="b">
+      <c r="H2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:23:38.366332+08:00</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:40:53.776257+08:00</t>
         </is>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="K2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="M2" s="2" t="n">
         <v>1926</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N2" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="O2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="P2" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q2" s="4" t="n">
+      <c r="Q2" s="2" t="n">
         <v>1976</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="R2" s="2" t="n">
         <v>1961</v>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
         </is>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="U2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="V2" s="2" t="n">
         <v>1961</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="W2" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="4" t="inlineStr"/>
-      <c r="AA2" s="4" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-25</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H3" s="4" t="b">
+      <c r="H3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:23:17.137147+08:00</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:40:12.120180+08:00</t>
         </is>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="M3" s="2" t="n">
         <v>2032</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="P3" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="Q3" s="2" t="n">
         <v>2089</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="R3" s="2" t="n">
         <v>2067</v>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
         </is>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="V3" s="2" t="n">
         <v>2067</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="W3" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr"/>
-      <c r="Z3" s="4" t="inlineStr"/>
-      <c r="AA3" s="4" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-24</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H4" s="4" t="b">
+      <c r="H4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T12:44:09.884829+08:00</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T13:04:34.984103+08:00</t>
         </is>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K4" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="M4" s="2" t="n">
         <v>3760</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="O4" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="P4" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="Q4" s="2" t="n">
         <v>3802</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="R4" s="2" t="n">
         <v>3825</v>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
         </is>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="V4" s="2" t="n">
         <v>3793</v>
       </c>
-      <c r="W4" s="4" t="n">
+      <c r="W4" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="X4" s="4" t="inlineStr"/>
-      <c r="Y4" s="4" t="inlineStr"/>
-      <c r="Z4" s="4" t="inlineStr"/>
-      <c r="AA4" s="4" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>ticker-audit</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:15:49.296780+08:00</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:15:49.296790+08:00</t>
         </is>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="n">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="n">
         <v>1691</v>
       </c>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="n">
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="Y5" s="4" t="n">
+      <c r="Y5" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="Z5" s="4" t="n">
+      <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2026-10-22T00:26:32.508450+08:00</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:26:32.508450+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="b">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:26:34.299718+08:00</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:32:11.776786+08:00</t>
         </is>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="O6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="P6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="Q6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="R6" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>['沿用已擷取資料；不重新抓取']</t>
         </is>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V6" s="4" t="n">
+      <c r="V6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="4" t="n">
+      <c r="W6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr"/>
-      <c r="Z6" s="4" t="inlineStr"/>
-      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H7" s="4" t="b">
+      <c r="H7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:20:47.845317+08:00</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:21:20.302846+08:00</t>
         </is>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="M7" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="O7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="P7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="4" t="n">
+      <c r="Q7" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="R7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
         </is>
       </c>
-      <c r="U7" s="4" t="n">
+      <c r="U7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="4" t="n">
+      <c r="V7" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="W7" s="4" t="n">
+      <c r="W7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr"/>
-      <c r="Z7" s="4" t="inlineStr"/>
-      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H8" s="4" t="b">
+      <c r="H8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="M8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="O8" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="P8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="Q8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="R8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="S8" s="4" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>['沿用已擷取資料；不重新抓取']</t>
         </is>
       </c>
-      <c r="U8" s="4" t="n">
+      <c r="U8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="4" t="n">
+      <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="4" t="n">
+      <c r="W8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="4" t="inlineStr"/>
-      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA8"/>

--- a/news_daily/2026-09-21.xlsx
+++ b/news_daily/2026-09-21.xlsx
@@ -1454,28 +1454,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1515,7 +1519,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1524,7 +1528,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>3f951b2de3aa4e429364b413853303a7</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>bc98077090826b8e08d0e5a4</t>
@@ -1545,7 +1553,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1589,10 +1601,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1628,28 +1652,32 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1689,7 +1717,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1698,7 +1726,11 @@
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>1796c37956f2415f99c35cbe6fc21c34</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>0f89c4f7092d29c6badbd804</t>
@@ -1719,7 +1751,11 @@
       <c r="AL6" s="2" t="inlineStr"/>
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="2" t="inlineStr"/>
       <c r="AQ6" s="2" t="inlineStr"/>
       <c r="AR6" s="2" t="inlineStr"/>
@@ -1763,10 +1799,22 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
